--- a/outputs/daily/hr_rankings_2026-10-24.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-24.xlsx
@@ -845,7 +845,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>52.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>34.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -910,12 +910,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>69.09</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>51.7</v>
+        <v>51.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="Q4" t="n">
         <v>36.5</v>
@@ -1527,7 +1527,7 @@
         <v>34.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.8</v>
+        <v>48.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>34.6</v>
       </c>
       <c r="S6" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -2224,12 +2224,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>48.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2523,7 +2523,7 @@
         <v>34.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.3</v>
+        <v>47</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2828,11 +2828,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38.2</v>
+        <v>47.1</v>
       </c>
       <c r="Q8" t="n">
         <v>28.5</v>
@@ -2841,13 +2841,13 @@
         <v>34.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>25.3</v>
+        <v>13.3</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2860,12 +2860,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -2932,72 +2932,72 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.6</v>
+        <v>44.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,11 +3464,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>47.1</v>
+        <v>39.5</v>
       </c>
       <c r="Q10" t="n">
         <v>28.5</v>
@@ -3477,13 +3477,13 @@
         <v>34.6</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>13.3</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3496,12 +3496,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -3553,87 +3553,87 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3768,7 +3768,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>44.7</v>
+        <v>43.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,11 +3782,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="Q11" t="n">
         <v>28.5</v>
@@ -3795,13 +3795,13 @@
         <v>34.6</v>
       </c>
       <c r="S11" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>37.8</v>
+        <v>25.3</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3876,12 +3876,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37</v>
+        <v>38.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -4113,7 +4113,7 @@
         <v>34.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.6</v>
+        <v>34.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>34.6</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.9</v>
+        <v>34.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,11 +4736,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q14" t="n">
         <v>36.5</v>
@@ -4749,13 +4749,13 @@
         <v>34.6</v>
       </c>
       <c r="S14" t="n">
-        <v>92.09999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4768,12 +4768,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -4845,67 +4845,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -4991,24 +4991,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -5021,17 +5021,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.8</v>
+        <v>34.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,26 +5054,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.5</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>28.5</v>
+        <v>36.5</v>
       </c>
       <c r="R15" t="n">
         <v>34.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>24.9</v>
+        <v>15.3</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5086,24 +5086,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -5148,112 +5148,112 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5358,7 +5358,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.6</v>
+        <v>31.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5376,22 +5376,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.5</v>
+        <v>26.9</v>
       </c>
       <c r="R16" t="n">
         <v>34.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>23.7</v>
+        <v>5.1</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5404,24 +5404,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -5451,12 +5451,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5481,67 +5481,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -5627,24 +5627,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -5657,17 +5657,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.2</v>
+        <v>30.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5690,26 +5690,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.4</v>
+        <v>28.5</v>
       </c>
       <c r="R17" t="n">
         <v>34.6</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>27</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5722,24 +5722,24 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5784,112 +5784,112 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5945,24 +5945,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -5975,17 +5975,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.1</v>
+        <v>30.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6008,26 +6008,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>36.5</v>
+        <v>28.5</v>
       </c>
       <c r="R18" t="n">
         <v>34.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6040,12 +6040,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6102,112 +6102,112 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -6263,24 +6263,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -6293,17 +6293,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.5</v>
+        <v>30.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6330,22 +6330,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>28.5</v>
+        <v>35.4</v>
       </c>
       <c r="R19" t="n">
         <v>34.6</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>17.3</v>
+        <v>27</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -6358,12 +6358,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -6405,12 +6405,12 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -6420,112 +6420,112 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>52.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>34.6</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -7082,12 +7082,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>69.09</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>51.7</v>
+        <v>51.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="Q4" t="n">
         <v>36.5</v>
@@ -7699,7 +7699,7 @@
         <v>34.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.8</v>
+        <v>48.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>34.6</v>
       </c>
       <c r="S6" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -8396,12 +8396,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>48.3</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -8695,7 +8695,7 @@
         <v>34.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8986,7 +8986,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>46.3</v>
+        <v>47</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9000,11 +9000,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38.2</v>
+        <v>47.1</v>
       </c>
       <c r="Q8" t="n">
         <v>28.5</v>
@@ -9013,13 +9013,13 @@
         <v>34.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>25.3</v>
+        <v>13.3</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -9032,12 +9032,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -9089,12 +9089,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -9104,72 +9104,72 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9622,7 +9622,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>45.6</v>
+        <v>44.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9636,11 +9636,11 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>47.1</v>
+        <v>39.5</v>
       </c>
       <c r="Q10" t="n">
         <v>28.5</v>
@@ -9649,13 +9649,13 @@
         <v>34.6</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>13.3</v>
+        <v>37.8</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9668,12 +9668,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -9725,87 +9725,87 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>44.7</v>
+        <v>43.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9954,11 +9954,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>39.5</v>
+        <v>38.2</v>
       </c>
       <c r="Q11" t="n">
         <v>28.5</v>
@@ -9967,13 +9967,13 @@
         <v>34.6</v>
       </c>
       <c r="S11" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>37.8</v>
+        <v>25.3</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9986,12 +9986,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -10063,67 +10063,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -10258,7 +10258,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37</v>
+        <v>38.2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -10285,7 +10285,7 @@
         <v>34.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -10304,12 +10304,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10576,7 +10576,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>36.6</v>
+        <v>34.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>34.6</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -10622,12 +10622,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10875,7 +10875,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.9</v>
+        <v>34.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10908,11 +10908,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q14" t="n">
         <v>36.5</v>
@@ -10921,13 +10921,13 @@
         <v>34.6</v>
       </c>
       <c r="S14" t="n">
-        <v>92.09999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10940,12 +10940,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -10987,12 +10987,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -11017,67 +11017,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -11163,24 +11163,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -11193,17 +11193,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.8</v>
+        <v>34.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,26 +11226,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.5</v>
+        <v>0.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>28.5</v>
+        <v>36.5</v>
       </c>
       <c r="R15" t="n">
         <v>34.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>24.9</v>
+        <v>15.3</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11258,24 +11258,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -11310,7 +11310,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -11320,112 +11320,112 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -11530,7 +11530,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.6</v>
+        <v>31.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11548,22 +11548,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.5</v>
+        <v>26.9</v>
       </c>
       <c r="R16" t="n">
         <v>34.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>23.7</v>
+        <v>5.1</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11576,24 +11576,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
@@ -11623,12 +11623,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -11638,12 +11638,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11653,67 +11653,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -11799,24 +11799,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -11829,17 +11829,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -11848,7 +11848,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.2</v>
+        <v>30.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11862,26 +11862,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.4</v>
+        <v>28.5</v>
       </c>
       <c r="R17" t="n">
         <v>34.6</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>27</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11894,24 +11894,24 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11956,112 +11956,112 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -12117,24 +12117,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>810938</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ben Williamson</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -12147,17 +12147,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.1</v>
+        <v>30.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12180,26 +12180,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.6</v>
+        <v>11.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>36.5</v>
+        <v>28.5</v>
       </c>
       <c r="R18" t="n">
         <v>34.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>23.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12212,12 +12212,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -12259,12 +12259,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12274,112 +12274,112 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>98.4446</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0789</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2809</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.49</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.0731</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -12435,24 +12435,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -12465,17 +12465,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -12484,7 +12484,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.5</v>
+        <v>30.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12502,22 +12502,22 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>28.5</v>
+        <v>35.4</v>
       </c>
       <c r="R19" t="n">
         <v>34.6</v>
       </c>
       <c r="S19" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>17.3</v>
+        <v>27</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -12592,112 +12592,112 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-24.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-24.xlsx
@@ -840,12 +840,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52.5</v>
+        <v>53.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>34.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -905,39 +905,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1158,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1182,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.1</v>
+        <v>52.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1196,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1209,7 +1205,7 @@
         <v>34.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1223,39 +1219,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1400,7 +1392,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1476,12 +1468,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1500,7 +1492,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1514,7 +1506,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1527,7 +1519,7 @@
         <v>34.6</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1543,39 +1535,35 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1720,7 +1708,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1836,7 +1824,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1860,7 +1848,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49</v>
+        <v>49.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1874,7 +1862,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1887,7 +1875,7 @@
         <v>34.6</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -1901,39 +1889,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2078,7 +2062,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2129,24 +2113,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -2154,22 +2138,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2178,7 +2162,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.4</v>
+        <v>47</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2192,26 +2176,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>43.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>36.5</v>
+        <v>28.5</v>
       </c>
       <c r="R6" t="n">
         <v>34.6</v>
       </c>
       <c r="S6" t="n">
-        <v>71.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>54.9</v>
+        <v>25.3</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -2219,39 +2203,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2271,12 +2251,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2286,117 +2266,117 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2472,12 +2452,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2496,7 +2476,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.3</v>
+        <v>47</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2510,7 +2490,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2523,7 +2503,7 @@
         <v>34.6</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2537,39 +2517,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2714,7 +2690,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2765,24 +2741,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -2790,22 +2766,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2814,7 +2790,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47</v>
+        <v>46.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2828,26 +2804,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>47.1</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.5</v>
+        <v>36.5</v>
       </c>
       <c r="R8" t="n">
         <v>34.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>13.3</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2855,39 +2831,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2907,12 +2879,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2922,117 +2894,117 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3083,24 +3055,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -3108,22 +3080,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3132,7 +3104,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.9</v>
+        <v>46.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3146,26 +3118,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>41</v>
+        <v>47.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>36.5</v>
+        <v>28.5</v>
       </c>
       <c r="R9" t="n">
         <v>34.6</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>20.9</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -3173,39 +3145,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3225,12 +3193,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -3240,117 +3208,117 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3401,24 +3369,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -3426,22 +3394,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3450,7 +3418,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.7</v>
+        <v>45.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3464,26 +3432,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>43.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>28.5</v>
+        <v>36.5</v>
       </c>
       <c r="R10" t="n">
         <v>34.6</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>54.9</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -3491,39 +3459,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3543,12 +3507,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -3558,117 +3522,117 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3719,12 +3683,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3744,12 +3708,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3768,7 +3732,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.5</v>
+        <v>45.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3782,11 +3746,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q11" t="n">
         <v>28.5</v>
@@ -3795,13 +3759,13 @@
         <v>34.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -3809,39 +3773,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3861,7 +3821,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3876,12 +3836,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3891,67 +3851,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -3986,7 +3946,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4037,12 +3997,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4062,12 +4022,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -4086,7 +4046,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.2</v>
+        <v>38.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4100,11 +4060,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>15.4</v>
       </c>
       <c r="Q12" t="n">
         <v>36.5</v>
@@ -4113,7 +4073,7 @@
         <v>34.6</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -4127,39 +4087,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4179,12 +4135,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -4194,7 +4150,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -4209,67 +4165,67 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -4304,7 +4260,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4355,12 +4311,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4380,12 +4336,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4404,7 +4360,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.9</v>
+        <v>37.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4418,11 +4374,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
         <v>36.5</v>
@@ -4431,13 +4387,13 @@
         <v>34.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4445,39 +4401,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4497,27 +4449,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -4527,67 +4479,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -4622,7 +4574,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4673,12 +4625,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4698,12 +4650,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4722,7 +4674,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34.6</v>
+        <v>36.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4736,11 +4688,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
         <v>36.5</v>
@@ -4749,13 +4701,13 @@
         <v>34.6</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4763,39 +4715,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4815,12 +4763,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -4830,7 +4778,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -4845,67 +4793,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -4940,7 +4888,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4991,12 +4939,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5016,12 +4964,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -5040,7 +4988,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.5</v>
+        <v>35.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5054,11 +5002,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.2</v>
+        <v>10.6</v>
       </c>
       <c r="Q15" t="n">
         <v>36.5</v>
@@ -5067,13 +5015,13 @@
         <v>34.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>15.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -5081,39 +5029,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5133,27 +5077,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -5163,67 +5107,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -5258,7 +5202,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5309,12 +5253,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5334,12 +5278,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -5358,7 +5302,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5372,26 +5316,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>26.9</v>
+        <v>28.5</v>
       </c>
       <c r="R16" t="n">
         <v>34.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5399,39 +5343,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5451,12 +5391,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -5466,12 +5406,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -5481,67 +5421,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -5576,7 +5516,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5627,12 +5567,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5652,12 +5592,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5676,7 +5616,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5690,11 +5630,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q17" t="n">
         <v>28.5</v>
@@ -5703,13 +5643,13 @@
         <v>34.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5717,42 +5657,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -5769,12 +5705,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5784,12 +5720,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -5799,67 +5735,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -5894,7 +5830,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5945,24 +5881,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -5970,7 +5906,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5980,12 +5916,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5994,7 +5930,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6008,26 +5944,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>28.5</v>
+        <v>35.4</v>
       </c>
       <c r="R18" t="n">
         <v>34.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>23.7</v>
+        <v>27</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -6035,39 +5971,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6087,12 +6019,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6102,117 +6034,117 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6263,24 +6195,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -6288,22 +6220,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -6326,26 +6258,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>35.4</v>
+        <v>28.5</v>
       </c>
       <c r="R19" t="n">
         <v>34.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>17.3</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -6353,39 +6285,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6405,12 +6333,12 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -6420,117 +6348,117 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -7012,12 +6940,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7036,7 +6964,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52.5</v>
+        <v>53.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7050,7 +6978,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7063,7 +6991,7 @@
         <v>34.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -7077,39 +7005,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7254,7 +7178,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7330,7 +7254,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7354,7 +7278,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>52.1</v>
+        <v>52.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7368,7 +7292,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7381,7 +7305,7 @@
         <v>34.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -7395,39 +7319,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7572,7 +7492,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7648,12 +7568,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -7672,7 +7592,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7686,7 +7606,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7699,7 +7619,7 @@
         <v>34.6</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -7715,39 +7635,35 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7892,7 +7808,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -8008,7 +7924,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -8032,7 +7948,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49</v>
+        <v>49.6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -8046,7 +7962,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -8059,7 +7975,7 @@
         <v>34.6</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -8073,39 +7989,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8250,7 +8162,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8301,24 +8213,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -8326,22 +8238,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -8350,7 +8262,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>48.4</v>
+        <v>47</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8364,26 +8276,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>43.6</v>
+        <v>38.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>36.5</v>
+        <v>28.5</v>
       </c>
       <c r="R6" t="n">
         <v>34.6</v>
       </c>
       <c r="S6" t="n">
-        <v>71.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>54.9</v>
+        <v>25.3</v>
       </c>
       <c r="V6" t="n">
         <v>50</v>
@@ -8391,39 +8303,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8443,12 +8351,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -8458,117 +8366,117 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>32.46</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8644,12 +8552,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8668,7 +8576,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>48.3</v>
+        <v>47</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8682,7 +8590,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -8695,7 +8603,7 @@
         <v>34.6</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -8709,39 +8617,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8886,7 +8790,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8937,24 +8841,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -8962,22 +8866,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -8986,7 +8890,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>47</v>
+        <v>46.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -9000,26 +8904,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>47.1</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.5</v>
+        <v>36.5</v>
       </c>
       <c r="R8" t="n">
         <v>34.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>13.3</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -9027,39 +8931,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9079,12 +8979,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -9094,117 +8994,117 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9255,24 +9155,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -9280,22 +9180,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -9304,7 +9204,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>45.9</v>
+        <v>46.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9318,26 +9218,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>41</v>
+        <v>47.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>36.5</v>
+        <v>28.5</v>
       </c>
       <c r="R9" t="n">
         <v>34.6</v>
       </c>
       <c r="S9" t="n">
-        <v>88.7</v>
+        <v>76.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>20.9</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -9345,39 +9245,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9397,12 +9293,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -9412,117 +9308,117 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9573,24 +9469,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -9598,22 +9494,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -9622,7 +9518,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.7</v>
+        <v>45.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9636,26 +9532,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.5</v>
+        <v>43.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>28.5</v>
+        <v>36.5</v>
       </c>
       <c r="R10" t="n">
         <v>34.6</v>
       </c>
       <c r="S10" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>37.8</v>
+        <v>54.9</v>
       </c>
       <c r="V10" t="n">
         <v>50</v>
@@ -9663,39 +9559,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9715,12 +9607,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -9730,117 +9622,117 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>32.46</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9891,12 +9783,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9916,12 +9808,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9940,7 +9832,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>43.5</v>
+        <v>45.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9954,11 +9846,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q11" t="n">
         <v>28.5</v>
@@ -9967,13 +9859,13 @@
         <v>34.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V11" t="n">
         <v>50</v>
@@ -9981,39 +9873,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10033,7 +9921,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -10048,12 +9936,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -10063,67 +9951,67 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10158,7 +10046,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10209,12 +10097,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10234,12 +10122,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -10258,7 +10146,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38.2</v>
+        <v>38.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10272,11 +10160,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>15.4</v>
       </c>
       <c r="Q12" t="n">
         <v>36.5</v>
@@ -10285,7 +10173,7 @@
         <v>34.6</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -10299,39 +10187,35 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10351,12 +10235,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -10366,7 +10250,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -10381,67 +10265,67 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -10476,7 +10360,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10527,12 +10411,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10552,12 +10436,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10576,7 +10460,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.9</v>
+        <v>37.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10590,11 +10474,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
         <v>36.5</v>
@@ -10603,13 +10487,13 @@
         <v>34.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10617,39 +10501,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10669,27 +10549,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -10699,67 +10579,67 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -10794,7 +10674,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10845,12 +10725,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10870,12 +10750,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -10894,7 +10774,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34.6</v>
+        <v>36.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10908,11 +10788,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
         <v>36.5</v>
@@ -10921,13 +10801,13 @@
         <v>34.6</v>
       </c>
       <c r="S14" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10935,39 +10815,35 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10987,12 +10863,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -11002,7 +10878,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -11017,67 +10893,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -11112,7 +10988,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11163,12 +11039,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11188,12 +11064,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -11212,7 +11088,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>34.5</v>
+        <v>35.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11226,11 +11102,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.2</v>
+        <v>10.6</v>
       </c>
       <c r="Q15" t="n">
         <v>36.5</v>
@@ -11239,13 +11115,13 @@
         <v>34.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>15.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>50</v>
@@ -11253,39 +11129,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11305,27 +11177,27 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -11335,67 +11207,67 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -11430,7 +11302,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11481,12 +11353,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11506,12 +11378,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -11530,7 +11402,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11544,26 +11416,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>16.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>26.9</v>
+        <v>28.5</v>
       </c>
       <c r="R16" t="n">
         <v>34.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>5.1</v>
+        <v>24.9</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11571,39 +11443,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11623,12 +11491,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -11638,12 +11506,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -11653,67 +11521,67 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -11748,7 +11616,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11799,12 +11667,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11824,12 +11692,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -11848,7 +11716,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11862,11 +11730,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q17" t="n">
         <v>28.5</v>
@@ -11875,13 +11743,13 @@
         <v>34.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11889,42 +11757,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -11941,12 +11805,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11956,12 +11820,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -11971,67 +11835,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -12066,7 +11930,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12117,24 +11981,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -12142,7 +12006,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -12152,12 +12016,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -12166,7 +12030,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12180,26 +12044,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>28.5</v>
+        <v>35.4</v>
       </c>
       <c r="R18" t="n">
         <v>34.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>23.7</v>
+        <v>27</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12207,39 +12071,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12259,12 +12119,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12274,117 +12134,117 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>35.67</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12435,24 +12295,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-25T00:00:00Z</t>
@@ -12460,22 +12320,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -12498,26 +12358,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>35.4</v>
+        <v>28.5</v>
       </c>
       <c r="R19" t="n">
         <v>34.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>17.3</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -12525,39 +12385,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12577,12 +12433,12 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -12592,117 +12448,117 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>103 deg</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
